--- a/data/dividends_info_20260720.xlsx
+++ b/data/dividends_info_20260720.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>54.31999969482422</v>
+        <v>54.90999984741211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.16568483156412</v>
+        <v>0.1639045715718422</v>
       </c>
       <c r="J2" t="n">
         <v>238</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.15000152587891</v>
+        <v>64.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.091192491581799</v>
+        <v>1.092043707743002</v>
       </c>
       <c r="J3" t="n">
         <v>217</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.159999847412109</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6550218449725329</v>
+        <v>0.6564551175737441</v>
       </c>
       <c r="J4" t="n">
         <v>147</v>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>54.34000015258789</v>
+        <v>54.90999984741211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1656238493693008</v>
+        <v>0.1639045715718422</v>
       </c>
       <c r="J6" t="n">
         <v>147</v>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.150000095367432</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I7" t="n">
-        <v>3.58139518997746</v>
+        <v>3.632075667763242</v>
       </c>
       <c r="J7" t="n">
         <v>126</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.63500022888184</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.247977800525101</v>
+        <v>1.247689499146453</v>
       </c>
       <c r="J8" t="n">
         <v>126</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.03000020980835</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I9" t="n">
-        <v>3.31674947000303</v>
+        <v>3.327786894896843</v>
       </c>
       <c r="J9" t="n">
         <v>119</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.820000171661377</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8591065038702054</v>
+        <v>0.8620689371678274</v>
       </c>
       <c r="J12" t="n">
         <v>77</v>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.63500022888184</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="I14" t="n">
-        <v>1.247977800525101</v>
+        <v>1.247689499146453</v>
       </c>
       <c r="J14" t="n">
         <v>63</v>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>54.34000015258789</v>
+        <v>54.90999984741211</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1656238493693008</v>
+        <v>0.1639045715718422</v>
       </c>
       <c r="J15" t="n">
         <v>63</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>92.69999694824219</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="I16" t="n">
-        <v>1.43473575381301</v>
+        <v>1.456735986357005</v>
       </c>
       <c r="J16" t="n">
         <v>63</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.900000095367432</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I17" t="n">
-        <v>5.08474568052218</v>
+        <v>5.263158070853988</v>
       </c>
       <c r="J17" t="n">
         <v>56</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.799999952316284</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="I20" t="n">
-        <v>5.284607232853467</v>
+        <v>5.265800818972078</v>
       </c>
       <c r="J20" t="n">
         <v>14</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.820000171661377</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I21" t="n">
-        <v>4.295532519351027</v>
+        <v>4.325259358568248</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>27.84000015258789</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5028735604621978</v>
+        <v>3.414634225767048</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9.907999992370605</v>
+        <v>9.899999618530273</v>
       </c>
       <c r="I23" t="n">
-        <v>2.624142109408621</v>
+        <v>2.626262727458558</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>13.47999954223633</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="I24" t="n">
-        <v>4.451038726819275</v>
+        <v>4.437869672226663</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.503999948501587</v>
+        <v>2.54200005531311</v>
       </c>
       <c r="I25" t="n">
-        <v>8.78594267270851</v>
+        <v>8.654602486737616</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6.545000076293945</v>
+        <v>6.565000057220459</v>
       </c>
       <c r="I27" t="n">
-        <v>1.527883863014776</v>
+        <v>1.523229232725076</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>19.04999923706055</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="I28" t="n">
-        <v>1.973753359887365</v>
+        <v>1.968586348117482</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.699999809265137</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="I30" t="n">
-        <v>2.105263228341595</v>
+        <v>2.101576168096538</v>
       </c>
       <c r="J30" t="n">
         <v>-7</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2.960000038146973</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="I32" t="n">
-        <v>5.067567502259338</v>
+        <v>5.102040717026832</v>
       </c>
       <c r="J32" t="n">
         <v>-7</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4.400000095367432</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="I34" t="n">
-        <v>1.590909056427066</v>
+        <v>1.521739161983556</v>
       </c>
       <c r="J34" t="n">
         <v>-14</v>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>35</v>
+        <v>34.29999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.4373177939838775</v>
       </c>
       <c r="J35" t="n">
         <v>-14</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>22.1200008392334</v>
+        <v>22</v>
       </c>
       <c r="I38" t="n">
-        <v>1.130198872129266</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="J38" t="n">
         <v>-28</v>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>28.20000076293945</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6914893429941666</v>
+        <v>0.6927175937566888</v>
       </c>
       <c r="J39" t="n">
         <v>-28</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.054999828338623</v>
+        <v>5.014999866485596</v>
       </c>
       <c r="I41" t="n">
-        <v>5.73689435901151</v>
+        <v>5.782652197820012</v>
       </c>
       <c r="J41" t="n">
         <v>-28</v>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.936000108718872</v>
+        <v>3.900000095367432</v>
       </c>
       <c r="I42" t="n">
-        <v>4.065040538123318</v>
+        <v>4.102564002243335</v>
       </c>
       <c r="J42" t="n">
         <v>-28</v>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.543999910354614</v>
+        <v>2.528000116348267</v>
       </c>
       <c r="I43" t="n">
-        <v>5.448113399527605</v>
+        <v>5.482594684378802</v>
       </c>
       <c r="J43" t="n">
         <v>-28</v>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>50.4900016784668</v>
+        <v>49.90499877929688</v>
       </c>
       <c r="I44" t="n">
-        <v>1.247771794526767</v>
+        <v>1.26239858813774</v>
       </c>
       <c r="J44" t="n">
         <v>-28</v>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.255000114440918</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="I45" t="n">
-        <v>2.238209391503959</v>
+        <v>2.272727329024459</v>
       </c>
       <c r="J45" t="n">
         <v>-28</v>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>27.6200008392334</v>
+        <v>27.59000015258789</v>
       </c>
       <c r="I47" t="n">
-        <v>3.07747999338436</v>
+        <v>3.080826369333208</v>
       </c>
       <c r="J47" t="n">
         <v>-28</v>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>54.34000015258789</v>
+        <v>54.90999984741211</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1656238493693008</v>
+        <v>0.1639045715718422</v>
       </c>
       <c r="J48" t="n">
         <v>-28</v>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.460000038146973</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6849314889533817</v>
+        <v>0.6711409353016787</v>
       </c>
       <c r="J49" t="n">
         <v>-28</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.197999954223633</v>
+        <v>6.193999767303467</v>
       </c>
       <c r="I50" t="n">
-        <v>2.92513716261732</v>
+        <v>2.927026264305596</v>
       </c>
       <c r="J50" t="n">
         <v>-28</v>
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.409999847412109</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I51" t="n">
-        <v>2.763018110691084</v>
+        <v>2.771854976842897</v>
       </c>
       <c r="J51" t="n">
         <v>-28</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10.22000026702881</v>
+        <v>10.22500038146973</v>
       </c>
       <c r="I52" t="n">
-        <v>2.710371749144096</v>
+        <v>2.709046353699837</v>
       </c>
       <c r="J52" t="n">
         <v>-28</v>
@@ -4331,7 +4331,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4341,14 +4341,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4358,14 +4358,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4382,7 +4382,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4399,7 +4399,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4545,14 +4545,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4562,14 +4562,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4586,7 +4586,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4596,14 +4596,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4620,7 +4620,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4647,14 +4647,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4664,14 +4664,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4681,14 +4681,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4698,14 +4698,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4715,14 +4715,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4756,7 +4756,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4834,14 +4834,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4851,14 +4851,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4875,7 +4875,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4926,7 +4926,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4970,14 +4970,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4987,14 +4987,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5004,14 +5004,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5072,14 +5072,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5096,7 +5096,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5106,14 +5106,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5140,14 +5140,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5164,7 +5164,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5181,7 +5181,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5191,14 +5191,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5208,14 +5208,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5232,7 +5232,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5242,14 +5242,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5293,14 +5293,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5334,7 +5334,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5344,14 +5344,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5378,14 +5378,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5419,7 +5419,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5436,7 +5436,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5453,7 +5453,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5538,7 +5538,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5616,14 +5616,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5640,7 +5640,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5650,14 +5650,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5667,14 +5667,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5691,7 +5691,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5725,7 +5725,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5735,14 +5735,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5752,14 +5752,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5786,14 +5786,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5810,7 +5810,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5820,14 +5820,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5844,7 +5844,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5854,14 +5854,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5929,7 +5929,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5939,14 +5939,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5963,7 +5963,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5997,7 +5997,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6007,14 +6007,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6058,14 +6058,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6092,14 +6092,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6126,14 +6126,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6160,14 +6160,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6177,14 +6177,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6201,7 +6201,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6218,7 +6218,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6235,7 +6235,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6245,14 +6245,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6279,14 +6279,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6296,14 +6296,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6313,14 +6313,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6337,7 +6337,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6371,7 +6371,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6381,14 +6381,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6405,7 +6405,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6422,7 +6422,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6439,7 +6439,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6473,7 +6473,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6500,14 +6500,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6568,14 +6568,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6592,7 +6592,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
